--- a/data/PTS_Registration_Exercise_Data_version_8.xlsx
+++ b/data/PTS_Registration_Exercise_Data_version_8.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://scottish-my.sharepoint.com/personal/dave_brand_sas_nhs_scot/Documents/Desktop/Bots/Systems Training DataBot/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{83787645-3C4F-467F-B1B2-8E73CEB3D3A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="8_{83787645-3C4F-467F-B1B2-8E73CEB3D3A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C841F48C-B19C-4A17-9D8B-58292DA1C26C}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="757" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -299,7 +299,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7972" uniqueCount="1186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7972" uniqueCount="1188">
   <si>
     <t>Exercise</t>
   </si>
@@ -3962,6 +3962,12 @@
   </si>
   <si>
     <t>ALISON MALCOLM</t>
+  </si>
+  <si>
+    <t>REGULAR BOOKING - MON/WED/FRI (RENAL PATIENT)</t>
+  </si>
+  <si>
+    <t>REGULAR BOOKING - TUE/THUR (CANCER PATIENT)</t>
   </si>
 </sst>
 </file>
@@ -16000,7 +16006,7 @@
         <v>118</v>
       </c>
       <c r="T2" s="5" t="s">
-        <v>119</v>
+        <v>323</v>
       </c>
       <c r="U2" s="5" t="s">
         <v>120</v>
@@ -16869,7 +16875,7 @@
       </c>
       <c r="S6" s="5"/>
       <c r="T6" s="5" t="s">
-        <v>119</v>
+        <v>323</v>
       </c>
       <c r="U6" s="5" t="s">
         <v>225</v>
@@ -19958,7 +19964,7 @@
         <v>117</v>
       </c>
       <c r="S20" s="5" t="s">
-        <v>494</v>
+        <v>1186</v>
       </c>
       <c r="T20" s="6" t="s">
         <v>323</v>
@@ -20185,7 +20191,7 @@
         <v>117</v>
       </c>
       <c r="S21" s="5" t="s">
-        <v>507</v>
+        <v>1187</v>
       </c>
       <c r="T21" s="6" t="s">
         <v>323</v>
@@ -21404,7 +21410,7 @@
         <v>118</v>
       </c>
       <c r="T2" s="5" t="s">
-        <v>119</v>
+        <v>323</v>
       </c>
       <c r="U2" s="5" t="s">
         <v>120</v>
@@ -22301,7 +22307,7 @@
       </c>
       <c r="S6" s="5"/>
       <c r="T6" s="5" t="s">
-        <v>119</v>
+        <v>323</v>
       </c>
       <c r="U6" s="5" t="s">
         <v>225</v>
@@ -25500,7 +25506,7 @@
         <v>117</v>
       </c>
       <c r="S20" s="5" t="s">
-        <v>494</v>
+        <v>1186</v>
       </c>
       <c r="T20" s="5" t="s">
         <v>323</v>
@@ -25729,7 +25735,7 @@
         <v>117</v>
       </c>
       <c r="S21" s="5" t="s">
-        <v>507</v>
+        <v>1187</v>
       </c>
       <c r="T21" s="5" t="s">
         <v>323</v>
@@ -49119,26 +49125,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
-  <documentManagement>
-    <TaxCatchAll xmlns="4442bde8-3b9a-412f-bffa-98aaf5709b6b" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="25793f7a-a37b-4e1c-b9fe-39e28de9fedb">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B4308F779970F84C843AB55D933EB081" ma:contentTypeVersion="37" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="19f4084aaceb61870d18cc023dcb3540">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="25793f7a-a37b-4e1c-b9fe-39e28de9fedb" xmlns:ns3="4442bde8-3b9a-412f-bffa-98aaf5709b6b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b7957b5a71a87a4ae3a73668c9525fc5" ns2:_="" ns3:_="">
     <xsd:import namespace="25793f7a-a37b-4e1c-b9fe-39e28de9fedb"/>
@@ -49399,32 +49385,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{476528D0-84CA-43FE-ADBE-AC70F915AFEA}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="4442bde8-3b9a-412f-bffa-98aaf5709b6b"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="25793f7a-a37b-4e1c-b9fe-39e28de9fedb"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AAA2B8A5-F530-4EC9-8F62-31FE373DE87B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
+  <documentManagement>
+    <TaxCatchAll xmlns="4442bde8-3b9a-412f-bffa-98aaf5709b6b" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="25793f7a-a37b-4e1c-b9fe-39e28de9fedb">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{54491E79-64EF-4A35-83EE-6A99F130AF57}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -49443,6 +49424,31 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AAA2B8A5-F530-4EC9-8F62-31FE373DE87B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{476528D0-84CA-43FE-ADBE-AC70F915AFEA}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="4442bde8-3b9a-412f-bffa-98aaf5709b6b"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="25793f7a-a37b-4e1c-b9fe-39e28de9fedb"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{b4199b9c-a89e-442f-9799-431511f14748}" enabled="1" method="Privileged" siteId="{10efe0bd-a030-4bca-809c-b5e6745e499a}" removed="0"/>
